--- a/exemple-ePrescription/ig/StructureDefinition-fr-cda-transport-du-patient.xlsx
+++ b/exemple-ePrescription/ig/StructureDefinition-fr-cda-transport-du-patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$96</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2680" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="374">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T08:51:06+00:00</t>
+    <t>2026-05-06T11:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -523,11 +523,133 @@
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-mode-de-transport-cisis</t>
   </si>
   <si>
-    <t>Act.text</t>
+    <t>Act.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Act.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Act.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Act.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Act.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Act.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Act.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Act.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Act.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
 </t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Act.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Act.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
+    <t>Act.text</t>
   </si>
   <si>
     <t>Texte décrivant le transport</t>
@@ -1381,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK85"/>
+  <dimension ref="A1:AK96"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.46484375" customWidth="true" bestFit="true"/>
@@ -4084,7 +4206,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>158</v>
       </c>
@@ -4103,7 +4225,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4288,7 +4410,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>165</v>
       </c>
@@ -4299,7 +4421,9 @@
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E29" s="2"/>
+      <c r="E29" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
@@ -4307,7 +4431,7 @@
         <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>74</v>
@@ -4316,12 +4440,12 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M29" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4347,13 +4471,11 @@
         <v>74</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>74</v>
@@ -4371,7 +4493,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4389,28 +4511,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4423,7 +4545,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4450,11 +4572,13 @@
         <v>74</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>74</v>
@@ -4472,7 +4596,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>89</v>
+        <v>168</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4490,7 +4614,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>169</v>
       </c>
@@ -4505,13 +4629,13 @@
         <v>170</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -4520,7 +4644,7 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
@@ -4551,29 +4675,31 @@
         <v>74</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4593,17 +4719,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4621,11 +4747,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4676,7 +4802,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4696,17 +4822,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4724,11 +4850,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4755,11 +4881,13 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>182</v>
+        <v>74</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -4777,7 +4905,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4795,19 +4923,19 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>80</v>
@@ -4816,7 +4944,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4825,11 +4953,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4880,7 +5008,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4900,18 +5028,16 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E35" t="s" s="2">
-        <v>189</v>
-      </c>
+      <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
@@ -4928,11 +5054,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4959,11 +5085,13 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>192</v>
+        <v>74</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -4981,7 +5109,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5001,10 +5129,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5027,10 +5155,12 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
+      <c r="M36" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5056,11 +5186,13 @@
         <v>74</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>195</v>
+        <v>74</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>74</v>
@@ -5078,7 +5210,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5098,16 +5230,18 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E37" s="2"/>
+      <c r="E37" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5124,17 +5258,13 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -5183,7 +5313,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5201,28 +5331,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5231,11 +5361,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5286,13 +5416,13 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>74</v>
@@ -5306,23 +5436,23 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -5334,11 +5464,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5389,13 +5519,13 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>74</v>
@@ -5407,12 +5537,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5426,7 +5556,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5435,9 +5565,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L40" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5464,11 +5596,13 @@
         <v>74</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y40" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>212</v>
+        <v>74</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>74</v>
@@ -5486,7 +5620,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5504,26 +5638,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E41" s="2"/>
+      <c r="E41" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F41" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5532,13 +5668,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>215</v>
+        <v>86</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5565,13 +5699,11 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>74</v>
@@ -5589,7 +5721,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>213</v>
+        <v>89</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5609,17 +5741,17 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>80</v>
@@ -5641,7 +5773,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>86</v>
+        <v>211</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5672,7 +5804,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>88</v>
+        <v>212</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -5690,7 +5822,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>89</v>
+        <v>213</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5710,16 +5842,18 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
@@ -5736,11 +5870,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5791,7 +5925,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5811,16 +5945,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
@@ -5841,12 +5977,12 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>223</v>
+        <v>74</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
@@ -5872,64 +6008,64 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AA44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>74</v>
@@ -5938,13 +6074,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5995,7 +6129,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6015,17 +6149,17 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
@@ -6043,11 +6177,11 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>234</v>
+        <v>85</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6074,13 +6208,11 @@
         <v>74</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>74</v>
+        <v>232</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>74</v>
@@ -6098,7 +6230,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6118,18 +6250,16 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" t="s" s="2">
-        <v>238</v>
-      </c>
+      <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
@@ -6146,12 +6276,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>239</v>
+        <v>85</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" t="s" s="2">
-        <v>240</v>
-      </c>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6177,13 +6305,11 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>74</v>
+        <v>235</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>74</v>
@@ -6201,7 +6327,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6219,28 +6345,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E48" t="s" s="2">
-        <v>243</v>
-      </c>
+      <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>74</v>
@@ -6249,15 +6373,17 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>228</v>
+        <v>102</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>74</v>
@@ -6306,7 +6432,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6324,26 +6450,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E49" s="2"/>
+      <c r="E49" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>74</v>
@@ -6352,10 +6480,12 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
+      <c r="M49" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6381,11 +6511,13 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>249</v>
+        <v>74</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6403,7 +6535,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6423,16 +6555,18 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
@@ -6449,10 +6583,12 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
+      <c r="M50" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6478,11 +6614,13 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>251</v>
+        <v>74</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -6520,10 +6658,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6546,7 +6684,7 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>253</v>
+        <v>91</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6575,13 +6713,11 @@
         <v>74</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>74</v>
+        <v>252</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>74</v>
@@ -6599,7 +6735,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6617,12 +6753,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6630,13 +6766,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>74</v>
@@ -6645,10 +6781,14 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
+      <c r="M52" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -6698,13 +6838,13 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>74</v>
@@ -6716,7 +6856,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>256</v>
       </c>
@@ -6727,7 +6867,9 @@
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E53" s="2"/>
+      <c r="E53" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
@@ -6735,7 +6877,7 @@
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6744,13 +6886,11 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>259</v>
+        <v>86</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6777,13 +6917,11 @@
         <v>74</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -6801,13 +6939,13 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>256</v>
+        <v>89</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>74</v>
@@ -6821,10 +6959,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6835,7 +6973,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
@@ -6847,10 +6985,12 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
+      <c r="M54" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6906,7 +7046,7 @@
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>74</v>
@@ -6920,10 +7060,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6934,7 +7074,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -6946,14 +7086,16 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>263</v>
+        <v>85</v>
       </c>
       <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
+      <c r="M55" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
-        <v>74</v>
+        <v>263</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
@@ -6975,13 +7117,11 @@
         <v>74</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>74</v>
+        <v>264</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -6999,13 +7139,13 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>74</v>
@@ -7019,21 +7159,23 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E56" s="2"/>
+      <c r="E56" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>151</v>
@@ -7045,13 +7187,13 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7102,13 +7244,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>74</v>
@@ -7120,26 +7262,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>74</v>
@@ -7148,13 +7292,11 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7205,13 +7347,13 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>74</v>
@@ -7225,17 +7367,17 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
@@ -7253,11 +7395,11 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>85</v>
+        <v>279</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>86</v>
+        <v>280</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7284,11 +7426,13 @@
         <v>74</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -7306,7 +7450,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>89</v>
+        <v>281</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7324,26 +7468,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" s="2"/>
+      <c r="E59" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>74</v>
@@ -7352,11 +7498,13 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L59" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="M59" t="s" s="2">
-        <v>92</v>
+        <v>285</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7407,13 +7555,13 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>93</v>
+        <v>286</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>74</v>
@@ -7427,10 +7575,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7453,12 +7601,10 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="L60" s="2"/>
-      <c r="M60" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -7484,13 +7630,11 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>74</v>
+        <v>289</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7508,7 +7652,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>97</v>
+        <v>287</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7520,7 +7664,7 @@
         <v>74</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>74</v>
@@ -7528,18 +7672,16 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E61" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
@@ -7556,12 +7698,10 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L61" s="2"/>
-      <c r="M61" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7591,7 +7731,7 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -7609,7 +7749,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>89</v>
+        <v>290</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7629,18 +7769,16 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E62" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
@@ -7657,12 +7795,10 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>102</v>
+        <v>293</v>
       </c>
       <c r="L62" s="2"/>
-      <c r="M62" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M62" s="2"/>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7712,7 +7848,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>104</v>
+        <v>292</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7732,23 +7868,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E63" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>74</v>
@@ -7760,12 +7894,10 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>107</v>
+        <v>295</v>
       </c>
       <c r="L63" s="2"/>
-      <c r="M63" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -7815,13 +7947,13 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>109</v>
+        <v>294</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>74</v>
@@ -7833,28 +7965,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E64" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -7863,11 +7993,13 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L64" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="M64" t="s" s="2">
-        <v>113</v>
+        <v>299</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7876,7 +8008,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>74</v>
@@ -7918,13 +8050,13 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>115</v>
+        <v>296</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>74</v>
@@ -7938,23 +8070,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E65" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>74</v>
@@ -7966,12 +8096,10 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>102</v>
+        <v>301</v>
       </c>
       <c r="L65" s="2"/>
-      <c r="M65" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8021,13 +8149,13 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>119</v>
+        <v>300</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>74</v>
@@ -8041,10 +8169,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8067,12 +8195,10 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>95</v>
+        <v>303</v>
       </c>
       <c r="L66" s="2"/>
-      <c r="M66" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8122,7 +8248,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>125</v>
+        <v>302</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8140,12 +8266,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8153,13 +8279,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>74</v>
@@ -8168,10 +8294,14 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8182,7 +8312,7 @@
         <v>74</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>281</v>
+        <v>74</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>74</v>
@@ -8197,11 +8327,13 @@
         <v>74</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>282</v>
+        <v>74</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>74</v>
@@ -8219,13 +8351,13 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>74</v>
@@ -8237,12 +8369,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8253,10 +8385,10 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>74</v>
@@ -8265,11 +8397,13 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L68" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="M68" t="s" s="2">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8281,7 +8415,7 @@
         <v>74</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>74</v>
@@ -8320,13 +8454,13 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>74</v>
@@ -8340,16 +8474,18 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E69" s="2"/>
+      <c r="E69" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
@@ -8366,16 +8502,16 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>288</v>
+        <v>86</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
-        <v>289</v>
+        <v>74</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
@@ -8397,13 +8533,11 @@
         <v>74</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>74</v>
@@ -8421,7 +8555,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>290</v>
+        <v>89</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8441,10 +8575,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8455,7 +8589,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>74</v>
@@ -8467,10 +8601,12 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
+      <c r="M70" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8520,13 +8656,13 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>292</v>
+        <v>93</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>74</v>
@@ -8540,10 +8676,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8566,10 +8702,12 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>294</v>
+        <v>95</v>
       </c>
       <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
+      <c r="M71" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8619,7 +8757,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>295</v>
+        <v>97</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8631,7 +8769,7 @@
         <v>74</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>74</v>
@@ -8639,16 +8777,18 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E72" s="2"/>
+      <c r="E72" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
@@ -8665,10 +8805,12 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>297</v>
+        <v>85</v>
       </c>
       <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
+      <c r="M72" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -8694,13 +8836,11 @@
         <v>74</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8718,7 +8858,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>298</v>
+        <v>89</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8738,16 +8878,18 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E73" s="2"/>
+      <c r="E73" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
@@ -8764,10 +8906,12 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>300</v>
+        <v>102</v>
       </c>
       <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
+      <c r="M73" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -8817,7 +8961,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>301</v>
+        <v>104</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8837,16 +8981,18 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E74" s="2"/>
+      <c r="E74" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
@@ -8863,10 +9009,12 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>303</v>
+        <v>107</v>
       </c>
       <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
+      <c r="M74" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -8916,7 +9064,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>304</v>
+        <v>109</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8936,18 +9084,20 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>75</v>
@@ -8962,10 +9112,12 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>306</v>
+        <v>112</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -8973,7 +9125,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>74</v>
@@ -9015,7 +9167,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>307</v>
+        <v>115</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9035,18 +9187,20 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E76" s="2"/>
+      <c r="E76" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>75</v>
@@ -9061,10 +9215,12 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>309</v>
+        <v>102</v>
       </c>
       <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
+      <c r="M76" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9114,7 +9270,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>310</v>
+        <v>119</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9134,10 +9290,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9148,7 +9304,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>74</v>
@@ -9160,10 +9316,12 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>312</v>
+        <v>95</v>
       </c>
       <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
+      <c r="M77" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9213,13 +9371,13 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>313</v>
+        <v>125</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>74</v>
@@ -9233,10 +9391,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9244,7 +9402,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>75</v>
@@ -9259,7 +9417,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>315</v>
+        <v>85</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9273,7 +9431,7 @@
         <v>74</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>74</v>
+        <v>321</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>74</v>
@@ -9288,13 +9446,11 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>74</v>
+        <v>322</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9312,10 +9468,10 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>75</v>
@@ -9332,10 +9488,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9358,10 +9514,12 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
+      <c r="M79" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9372,7 +9530,7 @@
         <v>74</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>74</v>
@@ -9411,7 +9569,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9431,10 +9589,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9457,14 +9615,16 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>321</v>
+        <v>107</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
+      <c r="M80" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
-        <v>74</v>
+        <v>329</v>
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
@@ -9510,7 +9670,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9530,10 +9690,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9556,7 +9716,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>324</v>
+        <v>107</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9609,7 +9769,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9629,10 +9789,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9643,7 +9803,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>74</v>
@@ -9655,7 +9815,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9708,13 +9868,13 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>74</v>
@@ -9728,10 +9888,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9742,7 +9902,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>74</v>
@@ -9754,7 +9914,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9807,13 +9967,13 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>74</v>
@@ -9827,10 +9987,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9841,7 +10001,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>74</v>
@@ -9853,7 +10013,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -9906,13 +10066,13 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>74</v>
@@ -9926,10 +10086,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9940,7 +10100,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>74</v>
@@ -9952,7 +10112,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10005,26 +10165,1115 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2"/>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L91" s="2"/>
+      <c r="M91" s="2"/>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK85" t="s" s="2">
+      <c r="H93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L96" s="2"/>
+      <c r="M96" s="2"/>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK96" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK85">
+  <autoFilter ref="A1:AK96">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10034,7 +11283,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
+  <conditionalFormatting sqref="A2:AI95">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
